--- a/promptDB/Anime Style.xlsx
+++ b/promptDB/Anime Style.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>원본 경로</t>
+          <t>메모</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -540,7 +540,6 @@
           <t>clip skip 2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>dpmpp_2m</t>
@@ -585,8 +584,6 @@
       <c r="H3" t="n">
         <v>7</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>euler_ancestral</t>
@@ -636,7 +633,6 @@
           <t>refiner: KSampler steps=8 cfg=2.0 denoise=0.3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>dpmpp_2m</t>

--- a/promptDB/Anime Style.xlsx
+++ b/promptDB/Anime Style.xlsx
@@ -126,6 +126,1495 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,7 +1906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -502,143 +1991,2599 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="96" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28 12:00</t>
+          <t>2026-07-29 19:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1girl, anime style, silver hair, blue eyes, school uniform, cherry blossom background, soft lighting, detailed face</t>
+          <t>A clean, expressive illustration style built on confident, simplified linework defining stylized, appealing proportions, flat-to-cel-based shading applied with straightforward graphic clarity, large expressive eyes carrying the primary emotional weight of the design, a bright, approachable simplicity that favors instant readability over rendering complexity, and a versatile, universally recognizable animated charm rooted in broad contemporary Japanese animation convention. Influenced by: contemporary anime illustration tradition, cel-shaded character-design technique, Japanese animation studio practice, mainstream manga-adaptation method.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lowres, bad anatomy, extra fingers, watermark, blurry</t>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>animagineXL_v31.safetensors</t>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>812374561</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>clip skip 2</t>
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Anime Style</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>dpmpp_2m</t>
+          <t>euler</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>karras</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="96" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-28 12:00</t>
+          <t>2026-07-29 19:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1boy, shounen anime style, black hair, red jacket, dynamic pose, city rooftop at sunset, dramatic rim light</t>
+          <t>A gentle, hand-painted animation illustration style built on soft watercolor-inspired shading that gives every plane a breathable, tender texture, meticulous naturalistic detail applied with unhurried patience, rounded, expressive proportions carrying quiet emotional sincerity, a hushed, wondrous stillness pervading even the most fantastical scenes, and a nostalgic, wholesome hand-crafted intensity that feels timeless and deeply human. Influenced by: Hayao Miyazaki, Studio Ghibli production technique, traditional cel-animation painting method, naturalist watercolor illustration tradition.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lowres, deformed hands, jpeg artifacts, text</t>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>animagineXL_v31.safetensors</t>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>27461903</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Ghibli Style</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>euler_ancestral</t>
+          <t>euler</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28 12:00</t>
+          <t>2026-07-29 19:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chibi character, pastel colors, simple background, sticker style, thick outline, cute expression</t>
+          <t>vintage Japanese animation aesthetics characterized by bold graphic draftsmanship, angular yet elegant character construction, expressive hand-drawn linework, simplified cel-painted rendering, dramatic visual staging, and a strong sense of romantic adventure. The style favors iconic silhouettes, emotional intensity, mechanical precision, and cinematic composition over contemporary polish, embracing the charm of traditional animation techniques, visible artistic craftsmanship, and classic storytelling sensibilities. Its visual identity balances dynamism, sincerity, and retro-futurist imagination, reminiscent of Leiji Matsumoto and Yoshikazu Yasuhiko, inspired by Space Battleship Yamato and Mobile Suit Gundam.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>realistic, photo, harsh shadows, cluttered background</t>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>animagineXL_v31.safetensors</t>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>559012388</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>70s Anime</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-29 19:59</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A clean, expressive black-and-white illustration style built on confident, precise linework defining stylized, appealing proportions, restrained tonal shading achieved through screentone patterning or fine cross-hatching rather than continuous gradation, large expressive eyes carrying much of the emotional weight, a dynamic, panel-ready clarity favoring instant visual readability, and a versatile, universally recognizable illustrative charm rooted in mainstream Japanese comic-illustration convention. Influenced by: mainstream manga illustration tradition, screentone-shading technique, Weekly Shōnen Jump publishing convention, Japanese comic-art practice.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Manga Style</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A meticulously detailed retro-futurist anime illustration style built on dense, precise linework rendering technology and urban decay with obsessive mechanical accuracy, flat cel-shaded color fields laid beneath sharp confident outline, dramatic neon and shadow contrast that carves gritty cyberpunk atmosphere across every surface, kinetic motion conveyed through bold speed-line dynamism, and a gritty, dystopian animation gravitas that feels both hand-crafted and technologically obsessive. Influenced by: Katsuhiro Otomo, 1980s cel-animation technique, cyberpunk anime tradition, retro-futurist manga illustration.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Akira Style</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>clean and highly readable linework, appealing character-focused design language, expressive forms, dynamic silhouettes, polished cel-style rendering, balanced stylization, energetic visual storytelling, strong graphic clarity, and a playful yet technically disciplined aesthetic that emphasizes personality and visual impact, reminiscent of Akira Toriyama and Toyotarou, inspired by Dragon Ball and Chrono Trigger.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>18</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Akira Toriyama Style</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bold graphic aesthetics characterized by sharp silhouette design, dynamic linework, stylized anatomy, exaggerated visual rhythm, striking contrast, and highly recognizable shape language, blending manga expressiveness with contemporary illustration sensibilities through energetic compositions, refined ink work, and a distinctive balance between elegance and intensity, reminiscent of Atsushi Ohkubo and Tite Kubo, inspired by Soul Eater and Fire Force.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Atsushi Ohkubo Style</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A gritty, high-tension manga-anime illustration style built on dense, realistic linework rendering musculature and gear with mechanical precision, dramatic dark shading and heavy cross-hatched texture that carves grim, intensity into every surface, dynamic extreme-perspective framing charged with kinetic urgency and scale, desaturated tonal harmony broken by stark high-contrast lighting in moments of violence or dread, and a grim, visceral action-illustration gravitas suffused with existential tension. Influenced by: Hajime Isayama, dark shōnen manga tradition, cel-shaded action-anime technique, gritty military-fantasy illustration.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Attack on Titan Style</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A raw, gritty manga-illustration style built on loose, aggressive linework carrying deliberately unpolished, visceral energy, stark high-contrast shading that swallows much of the composition in engulfing shadow , a chaotic, kinetic sense of motion charged with unpredictable, feral intensity, meticulous grotesque body-horror rendering balanced against darkly comedic character design, and a raw, unflinching contemporary shōnen edge that feels equal parts brutal and irreverently funny. Influenced by: Tatsuki Fujimoto, contemporary dark-shōnen manga tradition, raw ink-heavy illustration technique, body-horror action-manga practice.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Chainsaw Man Style</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A dynamic, high-contrast shōnen-manga illustration style built on confident, angular linework carrying sharp, kinetic action-driven posing, dense, moody shading with dramatic ink-heavy shadow blocking, a stylish, contemporary silhouette design balancing realism with graphic exaggeration, meticulous attention to fluid, high-impact motion within otherwise tightly controlled composition, and a fierce, cinematic shōnen intensity that feels equal parts stylish and visceral. Influenced by: Gege Akutami, MAPPA animation-adaptation tradition, cel-shaded dark-shōnen technique, contemporary action-manga character-design practice.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Jujutsu Kaisen Style</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A bold, dynamic shōnen-manga illustration style built on clean, confident linework carrying energetic, superhero-inspired posing, bright cel-based shading with punchy, graphic contrast reinforcing dramatic action, a hopeful, larger-than-life visual energy balanced against grounded emotional character work, meticulous costume and power-effect detail rendered with crisp graphic clarity, and an earnest, high-energy shōnen intensity that feels equal parts heroic spectacle and heartfelt coming-of-age drama. Influenced by: Kōhei Horikoshi, Studio Bones animation-adaptation tradition, cel-shaded superhero-manga technique, contemporary shōnen character-design practice.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>18</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>My Hero Academia Style</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>monumental dark fantasy manga aesthetics characterized by obsessive crosshatched detail, rugged textural density, dramatic black-and-white value structure, intricate ornamental craftsmanship, and an overwhelming sense of weight, scale, and historical depth. The style emphasizes brutal realism, weathered material rendering, architectural complexity, and emotionally intense visual storytelling, constructing imagery through countless layers of inked detail and highly disciplined draftsmanship. Rather than stylized simplification, it pursues visual immersion through realism, atmosphere, and relentless craftsmanship, creating artwork that feels ancient, tragic, and profoundly human. The visual language balances violence and beauty, grandeur and decay, with extraordinary attention to texture, structure, and narrative gravitas, reminiscent of Kentaro Miura and Hal Foster, inspired by Berserk and Prince Valiant.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>18</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Berserk Manga Style</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="96" customHeight="1">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A sleek, high-contrast shōnen-anime illustration style built on confident, angular linework carrying sharp, stylish silhouette design, bold cel-based shading with dramatic, graphic shadow blocking rather than smooth gradation, a moody, atmospheric restraint balanced against dynamic, action-charged posing, meticulous attention to elegant, flowing motion within otherwise crisp, controlled composition, and a stylish, brooding shōnen intensity that feels equal parts fashionable and fiercely kinetic. Influenced by: Tite Kubo, Studio Pierrot animation tradition, cel-shaded shōnen illustration technique, stylish action-anime character-design practice.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Bleach Style</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="96" customHeight="1">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A gentle, atmospheric anime-illustration style built on soft, delicate linework carrying a quiet, contemplative restraint, muted cel-based shading with subtle gradation rather than dramatic contrast, a hushed, melancholic stillness pervading even fantastical composition, meticulous attention to naturalistic environmental detail balanced against calm, understated character design, and a serene, wistful anime intensity that feels contemplative, tender, and quietly profound. Influenced by: Kanehito Yamada (original), Studio Madhouse animation-adaptation tradition, atmospheric anime-illustration technique, contemplative fantasy character-design practice.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Frieren Style</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="96" customHeight="1">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:04</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>A meticulously rendered manga-illustration style built on dense, hyper-precise linework that treats anatomy and mechanical detail with equal obsessive accuracy, dramatic high-contrast shading that carves powerful, sculptural form through confident cross-hatched shadow, a technically disciplined realism balancing muscular anatomical grounding with dynamic, kinetic posing, meticulous attention to material and structural logic rewarding close inspection, and a bold, technically virtuosic manga intensity that feels equal parts scientific precision and explosive physicality. Influenced by: Boichi, Dr. Stone manga art tradition, hyper-detailed manga illustration technique, technical-precision character-design practice.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>18</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Boichi Style</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="96" customHeight="1">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>premium animation aesthetics characterized by refined linework, sophisticated lighting design, cinematic composition, nuanced atmospheric depth, polished rendering, and emotionally driven visual storytelling, blending the clarity of high-end anime production with filmic realism through controlled detail, expressive staging, and exceptional artistic cohesion, reminiscent of Makoto Shinkai and Yoshiyuki Sadamoto, inspired by Your Name and Evangelion: 3.0+1.0 Thrice Upon a Time.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Cinematic Anime</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="96" customHeight="1">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:05</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>elegant manga-inspired aesthetics characterized by graceful linework, refined visual delicacy, expressive emotional storytelling, sophisticated composition, ornamental detailing, and a strong sense of romantic atmosphere, blending stylized beauty with polished illustration craftsmanship through airy visual rhythms, nuanced rendering, and timeless narrative charm, reminiscent of Riyoko Ikeda and CLAMP, inspired by The Rose of Versailles and Cardcaptor Sakura.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Classic Shojo Illustration</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="96" customHeight="1">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A hybrid illustration style built on Japanese manga-derived clean linework merged with European bande-dessinée compositional discipline, cel-based shading softened by more naturalistic tonal transition than typical manga convention, anatomically grounded proportions carrying a slightly more realistic weight than mainstream shōnen or shōjo tradition, meticulous, patient rendering of environment and costume detail rewarding close inspection, and a polished, cross-cultural illustration sensibility that bridges Eastern character-design fluency with Western graphic-novel craftsmanship. Influenced by: Franco-Belgian manga-influenced illustration movement, European graphic-novel tradition, hybrid manga-bande-dessinée technique, contemporary Euromanga publishing practice.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>18</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Euromanga Style</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="96" customHeight="1">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A soft, luminous illustration style built on delicate translucent washes blending seamlessly with clean anime-adjacent linework, gentle bleeding and diffusion at the edges lending each plane a tender, organic softness, restrained tonal layering achieved through patient, unhurried wash-building rather than opaque coverage, a hushed, dreamlike stillness carried through soft directional light, and a poetic, wistful character-illustration finish that feels equally hand-painted and anime-refined. Influenced by: traditional watercolor-and-wash technique, contemporary anime-illustration tradition, gentle wash-blending practice, semi-realistic character-art method.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Watercolor Anime Illustration</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="96" customHeight="1">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A richly detailed JRPG character-illustration style built on crisp painterly linework blended seamlessly into soft airbrushed shading, glossy semi-realistic rendering that gives skin and hair a polished, luminous finish without tipping into full photorealism, confident glamorous pin-up posing framed with clean graphic composition, delicately layered ornamental costume detail rendered with meticulous craftsmanship, and a vibrant, high-production mobile-gacha polish that feels equally at home as key art and collectible card illustration. Influenced by: Minaba Hideo, Cygames character-art direction, JRPG gacha illustration technique, semi-realistic anime rendering.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Granblue Fantasy Pin-Up Style</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="96" customHeight="1">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A ferociously energetic illustration style built on wild, gestural linework that captures raw movement and muscular dynamism in every stroke, loose ink-driven cross-hatching layered with confident painterly color, chaotic yet controlled compositions bursting with kinetic tension, richly textured surface detail giving textures a visceral, almost sculptural intensity, and a bold, untamed painterly ferocity that feels equally at home in fine art and manga tradition. Influenced by: Katsuya Terada, Japanese gekiga illustration, ink-and-color technique, fantasy creature illustration.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Katsuya Terada Style</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="96" customHeight="1">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A richly polished Korean digital-comic illustration style built on crisp, precise linework merged seamlessly with dense, meticulous rendering across skin, hair, and costume, exhaustive layered shading that builds photographic depth while retaining a clean, semi-realistic anime-adjacent finish, luminous soft-gradient highlights giving every surface a glossy, high-production sheen, obsessive attention to fine ornamental and textural detail rewarding close inspection, and a polished, high-stakes cinematic webtoon intensity built for full-screen serialized impact. Influenced by: Redice Studio digital-coloring technique, Korean manhwa production standard, semi-realistic webtoon rendering practice, high-detail digital-comic illustration tradition.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>18</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Manhwa Ultradetailed Art</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="96" customHeight="1">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A meticulously rendered manga-illustration style built on obsessive anatomical precision that treats musculature and material detail with near-photographic exactness, dramatic high-contrast shading carving powerful, sculptural form through confident cross-hatched shadow, a technically disciplined realism that pushes traditional manga linework toward hyperreal density, dynamic, kinetic posing charged with explosive physical presence, and a bold, virtuosic manga intensity that feels equal parts scientific precision and raw physical spectacle. Influenced by: Yusuke Murata, One-Punch Man manga tradition, hyper-detailed manga illustration technique, technical-precision character-design practice.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>18</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Murata Hyperrealism</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="96" customHeight="1">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="H4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>refiner: KSampler steps=8 cfg=2.0 denoise=0.3</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>dpmpp_2m</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A vibrant, painterly anime-fusion illustration style defined by luminous soft-gradient shading, glowing rim light and dreamy bloom haloing the figure, richly saturated color palettes that lean pastel-fantasy or neon-vivid by turns, delicate linework blended seamlessly into airbrushed color rather than hard-outlined cel shading, whimsical atmospheric particles or floating light motes drifting through the scene, and a lush, otherworldly polish that feels equally at home as a fantasy book cover or a modern anime key visual. Influenced by: Niji Journey model aesthetics, modern anime key visual art, Makoto Shinkai lighting style, digital gouache illustration.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>18</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>MidJourney Niji-Inspired Digital Illustration</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="96" customHeight="1">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A polished Korean webtoon illustration style rendered with soft cel-shaded gradients over cleanly inked linework, realistically proportioned yet subtly idealized figures with smooth, luminous skin and delicately blushed cheeks, expressive detailed eyes rendered with glossy multi-layered highlights, soft ambient studio-like lighting that keeps shadows gentle and skin tones warm, and a clean, contemporary digital-comic polish characteristic of modern webtoon romance and drama art. Influenced by: Shindol, Korean webtoon illustration, Manhwa digital coloring technique, romance webtoon art direction.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>18</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Shindol Style</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="96" customHeight="1">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:08</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A high-impact cinematic manhwa illustration style combining hyper-detailed digital rendering with dramatic low-angle, action-movie framing, richly saturated dark color palettes cut through by glowing violet, blue, or crimson, meticulously rendered textures with sharp specular highlighting, dynamic motion lines heightening a sense of raw power, and a sleek, high-production webtoon polish that reads as equal parts video-game key art and blockbuster action illustration. Influenced by: DUBU (Redice Studio), Solo Leveling webtoon art direction, Korean manhwa digital coloring technique, cinematic video-game concept art.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>18</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Solo Leveling Art</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="96" customHeight="1">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:09</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>A hybrid illustration style built on flat anime-derived linework pushed toward volumetric, near-photographic shading, smooth gradient rendering that gives skin and hair a soft three-dimensional depth while retaining crisp graphic outline at the edges, meticulously blended highlight transitions that bridge cel-shading simplicity with painterly light behavior, confident anatomical grounding that leans semi-realistic without abandoning stylized facial proportion, and a polished, technically ambitious rendering intensity that sits deliberately between flat illustration and full photorealism. Influenced by: checkpoint-trained diffusion-model 2.5D aesthetic, semi-realistic anime rendering tradition, gacha-game character-art technique, hybrid cel-to-painterly shading practice.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>18</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Pony 2.5D Realism</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="96" customHeight="1">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A raw, gritty manga-illustration style built on loose, aggressive linework carrying deliberately unpolished, visceral energy, stark high-contrast shading that swallows much of the composition in engulfing shadow , a chaotic, kinetic sense of motion charged with unpredictable, feral intensity, meticulous grotesque body-horror rendering balanced against darkly comedic character design, and a raw, unflinching contemporary shōnen edge that feels equal parts brutal and irreverently funny. Influenced by: Tatsuki Fujimoto, contemporary dark-shōnen manga tradition, raw ink-heavy illustration technique, body-horror action-manga practice.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>18</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Pony/Illustrious Checkpoint Style</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="96" customHeight="1">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>An ethereal, elongated illustration style built on delicate, flowing linework that stretches anatomy into graceful, almost weightless proportion, translucent layered washes that let ink and pigment bleed softly into one another rather than sit as flat color, a dreamlike fragility carried through sparse, deliberate mark-making surrounded by generous negative space, ornamental fine detail concentrated in hair and fabric while the broader form stays airy and unresolved, and a haunting, otherworldly elegance that feels simultaneously fragile and mythic. Influenced by: Yoshitaka Amano, Final Fantasy character-art tradition, ink-wash illustration technique, Vampire Hunter D illustration practice.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>18</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Yoshitaka Amano Style</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="96" customHeight="1">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:12</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ethereal fine art aesthetics characterized by calligraphic linework, graceful visual ambiguity, flowing ornamental forms, delicate painterly textures, and a dreamlike fusion of elegance and abstraction. The style favors suggestion over definition, using elongated proportions, layered decorative motifs, atmospheric negative space, and fluid visual rhythms to create imagery that feels poetic, otherworldly, and timeless. Rather than pursuing realism, it embraces expressive symbolism, visual fragility, and emotional resonance through sophisticated composition and refined artistic intuition. The result evokes the feeling of an illuminated myth, balancing luxury, mystery, and imagination with an unmistakably lyrical sensibility, reminiscent of Yoshitaka Amano and Erté, inspired by Vampire Hunter D and Final Fantasy VI concept artwork.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>18</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Yoshitaka Amano Fine Art</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="96" customHeight="1">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:13</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>A dark, meticulously detailed manga-illustration style built on dense, precise linework rendering both anatomy and psychological tension with obsessive control, dramatic high-contrast shading that carves stark, engulfing shadow across brooding, angular composition, a restrained, cerebral intensity conveyed through sharp facial modeling and calculated posing, richly rendered fine detail balanced against vast negative space charged with unspoken menace, and a somber, suspenseful gravitas that feels equal parts psychological thriller and gothic elegance. Influenced by: Takeshi Obata, dark shōnen-manga illustration tradition, high-contrast cel-shaded technique, psychological-thriller manga practice.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>18</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Death Note Style</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="96" customHeight="1">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:13</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>A flamboyant, hyper-stylized manga-illustration style built on exaggerated, statuesque anatomy carrying dramatic fashion-forward posing, bold, high-contrast linework rendering musculature with sculptural, almost architectural precision, saturated graphic patterning integrated directly into confident silhouette design, dynamic, theatrical composition charged with operatic intensity and flair, and a bold, unapologetically stylish shōnen extravagance that feels equal parts high fashion and larger-than-life spectacle. Influenced by: Hirohiko Araki, flamboyant shōnen-manga tradition, sculptural anatomical-illustration technique, theatrical fashion-forward character-design practice.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>18</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>JoJo's Bizarre Adventure Style</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="96" customHeight="1">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:14</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>A bold, expressive shōnen-manga illustration style built on confident, energetic linework carrying exaggerated, rubber-hose-adjacent proportion flexibility, dynamic, kinetic posing charged with over-the-top comedic and dramatic range in equal measure, simplified cel-based shading that prioritizes bold graphic readability over subtle gradation, richly imaginative silhouette design that pushes anatomy and costume into instantly iconic exaggeration, and an adventurous, larger-than-life shōnen energy that balances whimsical humor with genuine emotional weight. Influenced by: Eiichiro Oda, Weekly Shōnen Jump illustration tradition, cel-shaded anime-adaptation technique, adventure-shōnen character-design practice.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>18</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>One Piece Style</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="96" customHeight="1">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:14</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>A luminous, romantic shōjo-anime illustration style built on delicate, sparkling linework paired with soft cel shading punctuated by dreamy glow and starburst highlight accents, large, deeply detailed eyes carrying the emotional core of every expression, flowing, elongated proportions with a graceful, idealized elegance, decorative sparkle and floral motif woven lightly through hair and costume rendering, and a nostalgic, magical-girl radiance that feels tender, whimsical, and unmistakably 90s-shōjo. Influenced by: Naoko Takeuchi, 90s shōjo-anime tradition, magical-girl cel-animation technique, Toei Animation production practice.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>18</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Sailor Moon Style</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="96" customHeight="1">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:15</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A super-deformed illustration style built on drastically compressed proportion where the head dominates a tiny, simplified body, minimal, rounded linework carrying maximum cuteness with minimal detail, flat-to-cel-based shading applied with cheerful simplicity, oversized expressive eyes and features exaggerated for instant emotional charm, and an endearing, playful miniature intensity that feels irresistibly cute and effortlessly lighthearted. Influenced by: chibi/super-deformed anime tradition, kawaii character-design technique, gag-manga illustration practice, cute-culture Japanese comic method.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>18</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Chibi Anime</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="96" customHeight="1">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:15</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A polished, high-production anime-illustration style built on crisp, confident linework merged with meticulously blended cel-to-gradient shading, dramatic promotional-grade lighting establishing bold mood within a single striking composition, richly detailed costume and character rendering balanced against clean, poster-ready silhouette clarity, dynamic yet composed posing calibrated for maximum visual impact at a glance, and a polished, franchise-defining illustration intensity built for instant recognition and promotional impact. Influenced by: contemporary anime-production key-visual tradition, promotional illustration technique, franchise-defining character-art practice, high-production anime-studio rendering method.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>18</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Anime Key Visual</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="96" customHeight="1">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:15</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>A meticulously detailed horror-manga illustration style built on dense, obsessive fine linework and cross-hatching that renders skin, hair, and texture with unsettling hyper-precision, ordinary human forms twisted into spiraling, biologically wrong distortions and body horror, stark black-and-white contrast with pools of inky shadow swallowing the edges of the frame, wide unblinking eyes carrying quiet dawning dread, and a slow-building, deeply unsettling atmosphere of cosmic horror seeping into mundane settings. Influenced by: Junji Ito, Tomie and Uzumaki manga art, body-horror illustration, ink cross-hatching technique.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>18</v>
+      </c>
+      <c r="G38" t="n">
+        <v>8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Junji Ito Style</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="96" customHeight="1">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:16</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>polished anime-inspired artwork featuring clean linework, expressive design language, refined cel-shading, controlled stylization, appealing visual clarity, carefully structured forms, and high-quality rendering that balances readability with emotional impact, emphasizing professional animation aesthetics and contemporary illustration craftsmanship, reminiscent of Yoshiyuki Sadamoto and Shingo Abe, inspired by Neon Genesis Evangelion and Your Name.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>18</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Anime Illustration</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="96" customHeight="1">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:16</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>exceptionally dense manga aesthetics characterized by obsessive line fidelity, intricate textural rendering, advanced visual layering, meticulous hatch work, precise structural draftsmanship, and an extraordinary concentration of graphical information. The style emphasizes complexity, craftsmanship, and prolonged visual exploration, rewarding close inspection through micro-detail, architectural precision, elaborate costume design, and highly refined material interpretation. Rather than relying on simplified manga shorthand, it pursues visual richness, technical virtuosity, and immersive image construction while preserving strong readability and compositional control. The overall effect feels ambitious, authoritative, and intensely crafted, balancing narrative clarity with astonishing detail density and artistic dedication, reminiscent of Kentaro Miura and Tsutomu Nihei, inspired by Berserk and BLAME!.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>18</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Ultradetailed Manga Illustration</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="96" customHeight="1">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>A high-gloss digital illustration style merging ultrarealistic rendering of skin, hair, and fabric with idealized anime facial structure and expressive large eyes, glassy specular highlights coating lips, skin, and hair strands like fresh lacquer, a confident pin-up pose with exaggerated curves softened by airbrush-smooth shading gradients, vibrant saturated color palettes popping against clean or softly blurred backdrops, and a glossy, collectible-print polish that reads as equal parts anime key visual and glamour illustration. Influenced by: Range Murata, SakimiChan, gacha-game character art, airbrush pin-up illustration.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>18</v>
+      </c>
+      <c r="G41" t="n">
+        <v>8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Polished Ultrarealistic Anime Pin-Up</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="96" customHeight="1">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>A tenderly rendered illustration style built on impossibly fine, barely-there contour linework that whispers rather than defines, seamlessly merged with photographically convincing tonal depth and light behavior, a gentle, wistful softness carried through delicate gradient transition rather than any hard graphic edge, meticulous realism in structural modeling coexisting quietly with idealized anime-adjacent proportion, a hushed, sentimental intimacy pervading every composition, and a quietly luminous, emotionally tender finish that feels equally drawn and photographed. Influenced by: Ilya Kuvshinov, semi-realistic anime-illustration technique, photobashing rendering practice, contemporary romantic-portrait illustration method.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>18</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Thin Delicate Outline Romantic Anime-Photographic Hybrid</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="96" customHeight="1">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>A crisp, flat-shaded rendering style built on hard-edged tonal division that separates each plane of light and shadow into distinct, uniform steps rather than smooth gradation, confident bold outline holding every shape with graphic clarity, minimal color banding replacing any continuous blending, a clean, deliberate simplicity that mimics hand-drawn animation logic within a fully dimensional render, and a punchy, graphic-meets-dimensional intensity that feels stylized, crisp, and instantly readable. Influenced by: cel-shading rendering technique, non-photorealistic 3D-rendering practice, anime-adjacent toon-shader method, stylized game-rendering tradition.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>18</v>
+      </c>
+      <c r="G43" t="n">
+        <v>8</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Cel Shading</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="96" customHeight="1">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:18</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A vibrant, expressive anime-illustration style built on clean, confident linework carrying a distinctly whimsical, slightly exaggerated character sensibility, smooth cel-to-gradient shading blending polished anime rendering with playful, quirky proportion, a surreal, dreamlike compositional sensibility that mixes humor and melancholy within the same frame, meticulous attention to expressive, emotionally readable posing and gesture, and a distinctive, contemporary fan-art vibrancy that feels both technically polished and unmistakably personal. Influenced by: Khyleri, contemporary anime fan-art illustration tradition, semi-realistic cel-shaded technique, whimsical character-illustration practice.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>18</v>
+      </c>
+      <c r="G44" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Khyleri Style</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="96" customHeight="1">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:18</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>A soft, nostalgic retro-anime illustration style built on gentle, rounded linework carrying warm, understated charm, muted cel-based shading with restrained, naturalistic gradation applied by hand rather than digital blending, a hazy, film-grain-adjacent softness pervading every composition, delicate attention to expressive, large eyes rendered with a gentler, less angular sensibility than contemporary anime convention, and a wistful, retro-romantic sincerity that feels tender, sincere, and quietly of its era. Influenced by: Studio Pierrot and Sunrise 1980s animation tradition, retro cel-animation painting technique, hand-inked classic-anime illustration practice, vintage animation-cel rendering method.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>18</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>80s Anime Style</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="96" customHeight="1">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:19</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>A bright, clean animation-illustration style built on confident, simplified linework carrying appealing, rounded proportion, smooth cel-based shading applied with cheerful graphic clarity, expressive large eyes carrying much of the emotional warmth of the design, a vivid, high-energy compositional vibrancy favoring instant readability, and a wholesome, adventurous anime charm that feels bright, friendly, and unmistakably contemporary. Influenced by: OLM Inc. animation-production technique, contemporary anime cel-shaded illustration practice, Ken Sugimori character-design tradition, mainstream Japanese animation-studio method.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>18</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Modern Pokémon Anime Style</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="96" customHeight="1">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:19</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>An elegant, elongated shōjo-manga illustration style built on sweeping, fluid linework that stretches proportion into graceful, dramatic exaggeration, richly detailed, ornately layered rendering that treats intricate pattern-work with obsessive linear precision, delicate cross-hatched shading applied with restrained, refined subtlety, a hushed, theatrical elegance carried through elongated, willowy posing, and a dramatic, gothic-romantic manga intensity that feels lavish, sophisticated, and unmistakably distinctive. Influenced by: CLAMP, contemporary shōjo-manga illustration tradition, ornate linework technique, gothic-romantic character-design practice.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>18</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>CLAMP Style</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="96" customHeight="1">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:19</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>A bold, expressive shōnen-manga illustration style built on confident, energetic linework carrying dynamic, action-driven proportion, cel-based shading applied with punchy, graphic clarity rather than smooth gradation, high-impact composition, meticulous attention to fluid, high-speed motion balanced against grounded emotional character work. Influenced by: Masashi Kishimoto, Studio Pierrot animation-adaptation tradition, cel-shaded shōnen illustration technique, Naruto Manga, Boruto Manga, adventure-shōnen character-design practice.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>18</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Naruto Style</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="96" customHeight="1">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:20</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>A glossy, high-production character-illustration style built on crisp painterly linework blended seamlessly into soft airbrushed shading, richly luminous textures and rendering that reads as premium and collectible at a glance, confident dynamic vibes framed for maximum instant appeal within a compact card format, vibrant, high-polish mobile-game key-art sheen optimized for eye-catching showcase. Influenced by: Cygames art direction, Hoyoverse gacha illustration technique, semi-realistic anime rendering, mobile key-art production standard.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>18</v>
+      </c>
+      <c r="G49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Polished Mobile Gacha Style</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="96" customHeight="1">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:20</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>A bold, flat cartoon illustration style built on thick, confident outline holding simplified, blocky proportions, bright, evenly applied flat color with minimal shading complexity, an exaggerated, oversized-head simplicity favoring instant graphic readability over anatomical detail, a loose, wobbly linework carrying deliberately crude, comedic charm, and a cheeky, irreverent cartoon energy that feels playful, satirical, and effortlessly recognizable. Influenced by: Yoshito Usui, crayon Shin-Chan character style, Studio Shin-Ei Animation tradition, flat-color cartoon technique, satirical children's-cartoon character-design practice.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>18</v>
+      </c>
+      <c r="G50" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Crayon Shin-chan Style</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="96" customHeight="1">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:21</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>A refined, elegant anime-illustration style built on confident, restrained linework carrying a subtly stylized proportion, muted cel-based shading with delicate gradation rather than sharp contrast, and a sophisticated. Influenced by: Yoshiyuki Sadamoto, Studio Gainax animation-adaptation tradition, cel-shaded design technique, Neon Genesis Evangelion illustration practice.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>18</v>
+      </c>
+      <c r="G51" t="n">
+        <v>8</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Yoshiyuki Sadamoto Style</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="96" customHeight="1">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:21</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>A crisp, mechanically precise anime-illustration style built on confident, angular linework rendering paneled hardware with technical exactness, dense cel-based shading punctuated by sharp specular highlight along every mechanical contour, a dynamic, imposing scale conveyed through dramatic low-angle composition, meticulous attention to intricate joint and thruster detail rewarding close inspection, and a bold, cinematic mecha intensity that feels powerful, technical, and unmistakably kinetic. Influenced by: Yoshiyuki Sadamoto, Studio Gainax mecha-design tradition, technical cel-shaded illustration technique, Neon Genesis Evangelion mecha-illustration practice.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>18</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Mecha Anime Style</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="96" customHeight="1">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A charming, expressive manga-illustration style built on confident, rounded linework carrying a distinctly whimsical, animation-influenced simplicity, conveying deep emotional sincerity within otherwise simplified design, unmistakably classic. Influenced by: Osamu Tezuka, Astro boy, Black Jack manga, foundational manga-illustration tradition, early Japanese cel-animation technique,</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>18</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Osamu Tezuka Style</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="96" customHeight="1">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:22</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>A bold, expressive shōnen-manga illustration style built on confident, angular linework carrying dramatic, dynamic design, dense cel-based shading punctuated by sharp specular highlight detail, a theatrical, high-stakes intensity conveyed through dramatic composition, meticulous attention to costume and design rendering rewarding close inspection. Influenced by: Kazuki Takahashi, Yu-Gi-Oh! Anime, Studio Gallop animation, cel-shaded shōnen illustration technique,</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Krea2\krea2_raw_int8_convrot.safetensors</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>18</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Yu-Gi-Oh! Style</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>euler</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
@@ -646,5 +4591,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>